--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N64_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N64_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>36.26556312954659</v>
+        <v>5.893154008551321</v>
       </c>
       <c r="D2" t="n">
-        <v>37.18318071653613</v>
+        <v>6.042266866437121</v>
       </c>
       <c r="E2" t="n">
-        <v>11.03620877903025</v>
+        <v>1.793383926592415</v>
       </c>
       <c r="F2" t="n">
-        <v>7.782564933480746</v>
+        <v>1.264666801690621</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>8.915371048621493</v>
+        <v>1.448747795400993</v>
       </c>
       <c r="D3" t="n">
-        <v>22.4859972354984</v>
+        <v>3.653974550768489</v>
       </c>
       <c r="E3" t="n">
-        <v>11.03620877903025</v>
+        <v>1.793383926592415</v>
       </c>
       <c r="F3" t="n">
-        <v>7.782564933480746</v>
+        <v>1.264666801690621</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>19.86075198581094</v>
+        <v>3.227372197694278</v>
       </c>
       <c r="D4" t="n">
-        <v>27.77397223890841</v>
+        <v>4.513270488822616</v>
       </c>
       <c r="E4" t="n">
-        <v>11.03620877903025</v>
+        <v>1.793383926592415</v>
       </c>
       <c r="F4" t="n">
-        <v>7.782564933480746</v>
+        <v>1.264666801690621</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>32.99765326570461</v>
+        <v>5.362118655677</v>
       </c>
       <c r="D5" t="n">
-        <v>35.07817450707692</v>
+        <v>5.7002033574</v>
       </c>
       <c r="E5" t="n">
-        <v>11.03620877903025</v>
+        <v>1.793383926592415</v>
       </c>
       <c r="F5" t="n">
-        <v>7.782564933480746</v>
+        <v>1.264666801690621</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>29.60047361791781</v>
+        <v>4.810076962911645</v>
       </c>
       <c r="D6" t="n">
-        <v>30.79934780454979</v>
+        <v>5.00489401823934</v>
       </c>
       <c r="E6" t="n">
-        <v>11.03620877903025</v>
+        <v>1.793383926592415</v>
       </c>
       <c r="F6" t="n">
-        <v>7.782564933480746</v>
+        <v>1.264666801690621</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>23.64278408448176</v>
+        <v>3.841952413728287</v>
       </c>
       <c r="D7" t="n">
-        <v>30.13482314502107</v>
+        <v>4.896908761065925</v>
       </c>
       <c r="E7" t="n">
-        <v>11.03620877903025</v>
+        <v>1.793383926592415</v>
       </c>
       <c r="F7" t="n">
-        <v>7.782564933480746</v>
+        <v>1.264666801690621</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>33.23858014195932</v>
+        <v>5.401269273068389</v>
       </c>
       <c r="D8" t="n">
-        <v>35.45540346789925</v>
+        <v>5.761503063533628</v>
       </c>
       <c r="E8" t="n">
-        <v>11.03620877903025</v>
+        <v>1.793383926592415</v>
       </c>
       <c r="F8" t="n">
-        <v>7.782564933480746</v>
+        <v>1.264666801690621</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>10.30776406404415</v>
+        <v>1.675011660407175</v>
       </c>
       <c r="D9" t="n">
-        <v>24.40245686829054</v>
+        <v>3.965399241097213</v>
       </c>
       <c r="E9" t="n">
-        <v>11.03620877903025</v>
+        <v>1.793383926592415</v>
       </c>
       <c r="F9" t="n">
-        <v>7.782564933480746</v>
+        <v>1.264666801690621</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>2.183478446195428</v>
+        <v>0.354815247506757</v>
       </c>
       <c r="D10" t="n">
-        <v>34.06466407254322</v>
+        <v>5.535507911788273</v>
       </c>
       <c r="E10" t="n">
-        <v>11.03620877903025</v>
+        <v>1.793383926592415</v>
       </c>
       <c r="F10" t="n">
-        <v>7.782564933480746</v>
+        <v>1.264666801690621</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>31.24440016361698</v>
+        <v>5.07721502658776</v>
       </c>
       <c r="D11" t="n">
-        <v>32.52229163633299</v>
+        <v>5.284872390904111</v>
       </c>
       <c r="E11" t="n">
-        <v>11.03620877903025</v>
+        <v>1.793383926592415</v>
       </c>
       <c r="F11" t="n">
-        <v>7.782564933480746</v>
+        <v>1.264666801690621</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>22.38200540593665</v>
+        <v>3.637075878464706</v>
       </c>
       <c r="D12" t="n">
-        <v>23.40242394990005</v>
+        <v>3.802893891858759</v>
       </c>
       <c r="E12" t="n">
-        <v>11.03620877903025</v>
+        <v>1.793383926592415</v>
       </c>
       <c r="F12" t="n">
-        <v>7.782564933480746</v>
+        <v>1.264666801690621</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>12.94540589129922</v>
+        <v>2.103628457336123</v>
       </c>
       <c r="D13" t="n">
-        <v>13.34330931706177</v>
+        <v>2.168287764022538</v>
       </c>
       <c r="E13" t="n">
-        <v>11.03620877903025</v>
+        <v>1.793383926592415</v>
       </c>
       <c r="F13" t="n">
-        <v>7.782564933480746</v>
+        <v>1.264666801690621</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>16.62077013859466</v>
+        <v>2.700875147521633</v>
       </c>
       <c r="D14" t="n">
-        <v>19.94012626601328</v>
+        <v>3.240270518227157</v>
       </c>
       <c r="E14" t="n">
-        <v>11.03620877903025</v>
+        <v>1.793383926592415</v>
       </c>
       <c r="F14" t="n">
-        <v>7.782564933480746</v>
+        <v>1.264666801690621</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>19.34941788498228</v>
+        <v>3.144280406309621</v>
       </c>
       <c r="D15" t="n">
-        <v>17.8418637994388</v>
+        <v>2.899302867408806</v>
       </c>
       <c r="E15" t="n">
-        <v>11.03620877903025</v>
+        <v>1.793383926592415</v>
       </c>
       <c r="F15" t="n">
-        <v>7.782564933480746</v>
+        <v>1.264666801690621</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>25.82656062381019</v>
+        <v>4.196816101369156</v>
       </c>
       <c r="D16" t="n">
-        <v>24.68289011578982</v>
+        <v>4.010969643815846</v>
       </c>
       <c r="E16" t="n">
-        <v>11.03620877903025</v>
+        <v>1.793383926592415</v>
       </c>
       <c r="F16" t="n">
-        <v>7.782564933480746</v>
+        <v>1.264666801690621</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>31.36535135767704</v>
+        <v>5.096869595622518</v>
       </c>
       <c r="D17" t="n">
-        <v>30.82077652354926</v>
+        <v>5.008376185076755</v>
       </c>
       <c r="E17" t="n">
-        <v>11.03620877903025</v>
+        <v>1.793383926592415</v>
       </c>
       <c r="F17" t="n">
-        <v>7.782564933480746</v>
+        <v>1.264666801690621</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>18.74166481399131</v>
+        <v>3.045520532273589</v>
       </c>
       <c r="D18" t="n">
-        <v>38.1638974199015</v>
+        <v>6.201633330733993</v>
       </c>
       <c r="E18" t="n">
-        <v>11.03620877903025</v>
+        <v>1.793383926592415</v>
       </c>
       <c r="F18" t="n">
-        <v>7.782564933480746</v>
+        <v>1.264666801690621</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>25.83918209271354</v>
+        <v>4.198867090065949</v>
       </c>
       <c r="D19" t="n">
-        <v>22.97675121836881</v>
+        <v>3.733722072984933</v>
       </c>
       <c r="E19" t="n">
-        <v>11.03620877903025</v>
+        <v>1.793383926592415</v>
       </c>
       <c r="F19" t="n">
-        <v>7.782564933480746</v>
+        <v>1.264666801690621</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>36.59961455579316</v>
+        <v>5.947437365316389</v>
       </c>
       <c r="D20" t="n">
-        <v>34.90652976000209</v>
+        <v>5.672311086000339</v>
       </c>
       <c r="E20" t="n">
-        <v>11.03620877903025</v>
+        <v>1.793383926592415</v>
       </c>
       <c r="F20" t="n">
-        <v>7.782564933480746</v>
+        <v>1.264666801690621</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>42.74544866194526</v>
+        <v>6.946135407566105</v>
       </c>
       <c r="D21" t="n">
-        <v>41.53569825195871</v>
+        <v>6.749550965943291</v>
       </c>
       <c r="E21" t="n">
-        <v>11.03620877903025</v>
+        <v>1.793383926592415</v>
       </c>
       <c r="F21" t="n">
-        <v>7.782564933480746</v>
+        <v>1.264666801690621</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>45.75307251299834</v>
+        <v>7.43487428336223</v>
       </c>
       <c r="D22" t="n">
-        <v>43.42917165387994</v>
+        <v>7.057240393755491</v>
       </c>
       <c r="E22" t="n">
-        <v>11.03620877903025</v>
+        <v>1.793383926592415</v>
       </c>
       <c r="F22" t="n">
-        <v>7.782564933480746</v>
+        <v>1.264666801690621</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
